--- a/mappingCorps/ig/FRMedicationRequestLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRMedicationRequestLMCDAFHIR.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMTraitementPrescrit vers l'entrée CDA FRCDATraitementPrescrit, puis vers le profil FHIR FRMedicationRequestDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMPrescriptionItem vers l'entrée CDA FRCDATraitementPrescrit, puis vers le profil FHIR FRMedicationRequestDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +101,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement-prescrit</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-prescription-item</t>
   </si>
   <si>
     <t/>
@@ -109,7 +110,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement-prescrit</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit</t>
+    <t>FRLMPrescriptionItem</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,183 +119,198 @@
     <t>FRCDATraitementPrescrit</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.identifiant</t>
+    <t>FRLMPrescriptionItem.header.identifier</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.id</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.code</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.code</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.description</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.text</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.status</t>
+    <t>FRLMPrescriptionItem.header.status</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.statusCode</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.dureeTraitement</t>
+    <t>FRLMPrescriptionItem.header.author[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.author</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.medication</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.consumable</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.indication[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frReferenceInterne</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.periodOfUse</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.effectiveTime[not(@operator='A')]</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.frequenceAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.effectiveTime[@operator='A']</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.nombreRenouvellement</t>
+    <t>FRLMPrescriptionItem.dosageInstructions.renderedDosageInstruction</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.text</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.note</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frInstructionsAuPatient</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.effectiveTime.frequency</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency.period</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.effectiveTime.period</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.dateOfAdministration</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.conditionOfAdministration</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.precondition</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.duration</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.routeOfAdministration</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.routeCode</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.maxDoseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.maxLifetimeDose</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.quantityPrescribed</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frQuantiteDeProduit</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.validityPeriod</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frPeriodeDeRenouvellement</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.substitution.allowed[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frAutorisationSubstitution</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.numberOfRepeats</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.repeatNumber</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.voieAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.routeCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.regionAnatomique</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.approachSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.dose</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.rythmeAdministration</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.doseMaximale</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.maxDoseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.produitSante</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.consumable</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.prescripteur</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.author</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.auteur</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.motifTraitement</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frReferenceInterne</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.traitementPrescritSubordonnee</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frTraitementPrescritSubordonnee</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.referenceItemPlanTraitement</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frReferenceItemPlanTraitement</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.instructionsPatient</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frInstructionsAuPatient</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.instructionsDispensateur</t>
+    <t>FRLMPrescriptionItem.offLabel.isOffLabelUse</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frHorsAMM</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.note</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.entryRelationship:frInstructionsAuDispensateur</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.quantiteProduit</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frQuantiteDeProduit</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.autorisationSubstitution</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frAutorisationSubstitution</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.periodeRenouvellement</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frPeriodeDeRenouvellement</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.enRapportAvecALD</t>
+    <t>FRLMPrescriptionItem.enRapportAvecALD</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.entryRelationship:frEnRapportAvecALD</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.enRapportAvecAccidentTravail</t>
+    <t>FRLMPrescriptionItem.enRapportAvecAccidentTravail</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.entryRelationship:frEnRapportAvecAccidentTravail</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.enRapportAvecPrevention</t>
+    <t>FRLMPrescriptionItem.enRapportAvecPrevention</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.entryRelationship:frEnRapportAvecPrevention</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.nonRemboursable</t>
+    <t>FRLMPrescriptionItem.nonRemboursable</t>
   </si>
   <si>
     <t>FRCDATraitementPrescrit.entryRelationship:frNonRemboursable</t>
   </si>
   <si>
-    <t>FRLMTraitementPrescrit.horsAMM</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.entryRelationship:frHorsAMM</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.referencePrescription</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.frReferenceInterne.externalDocument</t>
-  </si>
-  <si>
-    <t>FRLMTraitementPrescrit.precondition</t>
-  </si>
-  <si>
-    <t>FRCDATraitementPrescrit.precondition</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-request-document</t>
   </si>
   <si>
@@ -304,88 +320,190 @@
     <t>FRMedicationRequestDocument.identifier</t>
   </si>
   <si>
-    <t>FRMedicationRequestDocument.note</t>
-  </si>
-  <si>
     <t>FRMedicationRequestDocument.status</t>
   </si>
   <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.boundsPeriod</t>
+    <t>FRMedicationRequestDocument.requester</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.extension:FRActorExtension</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.statusReason[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.statusReason</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.medication:FRMedicationDocument</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.reasonReference</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.text</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.effectiveTime.frequency</t>
+  </si>
+  <si>
+    <t>FRCDATraitementPrescrit.entryRelationship:frTraitement.entryRelationship:frTraitement.effectiveTime.period</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.text</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.sequence</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.sequence</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.patientInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat</t>
   </si>
   <si>
     <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.frequency</t>
   </si>
   <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.period</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.additionalInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.event</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.bounds[x]</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.duration.durationValue</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.duration</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.duration.durationUnit</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.durationUnit</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.duration.durationMax</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.durationMax</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.eventTime.eventTimeCode</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.when</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.dosageInstructions.dosageDetails.eventTime.offset</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.timing.repeat.offset</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.site</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.route</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.maxDosePerPeriod.numerator</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.maxDosePerPeriod.denominator</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dosageInstruction.maxDosePerLifetime</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dispenseRequest.quantity</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dispenseRequest.validityPeriod</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.substitution.allowedCodeableConcept</t>
+  </si>
+  <si>
+    <t>FRLMPrescriptionItem.substitution.reason[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.substitution.reason</t>
+  </si>
+  <si>
     <t>FRMedicationRequestDocument.dispenseRequest.numberOfRepeatsAllowed</t>
   </si>
   <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.route</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.site</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.doseAndRate.doseRange</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.doseAndRate.rateRange</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.maxDosePerPeriod</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.medication:FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.requester</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.extension:FRActorExtension</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.reasonReference</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.medication:FRMedicationsCombinaisonDocument</t>
-  </si>
-  <si>
-    <t>basedOn:FRMedicationRequestDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.additionalInstruction:instructionsPatient</t>
+    <t>FRLMPrescriptionItem.minimumDispenseInterval</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.dispenseRequest.dispenseInterval</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.extension:offLabelUse</t>
   </si>
   <si>
     <t>FRMedicationRequestDocument.dispenseRequest.extension:medicationRequest-dispenseRequest-dispenserInstruction-r5</t>
   </si>
   <si>
-    <t>FRMedicationRequestDocument.dispenseRequest.quantity</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.substitution.allowedCodeableConcept</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dispenseRequest.validityPeriod</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.reasonReference:ald</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.reasonReference:accidentTravail</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.reasonReference:prevention</t>
+    <t>FRMedicationRequestDocument.reasonReference:FRObservationALDDocument</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.reasonReference:FRObservationWorkRelatedAccidentDocument</t>
+  </si>
+  <si>
+    <t>FRMedicationRequestDocument.reasonReference:FRObservationPreventionDocument</t>
   </si>
   <si>
     <t>FRMedicationRequestDocument.extension:FRNotCoveredExtension</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.extension:FRMedicationRequestOutOfNomenclatureExtension</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.instantiatesUri</t>
-  </si>
-  <si>
-    <t>FRMedicationRequestDocument.dosageInstruction.additionalInstruction:precondition</t>
   </si>
 </sst>
 </file>
@@ -637,7 +755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -865,217 +983,308 @@
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1084,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1106,7 +1315,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -1115,7 +1324,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -1123,393 +1332,1178 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>116</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D17" t="s" s="2">
         <v>123</v>
       </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D50" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E50" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
